--- a/PUBLIC_PRIVATE_CHECKLIST.xlsx
+++ b/PUBLIC_PRIVATE_CHECKLIST.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R123300b3c0eb4e95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R1aef01082d52451d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rf173b6e78e1342b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R7f71eae8edae4225"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -500,12 +500,12 @@
         <x:v>GEO/HPA matrices are not redistributed; users obtain them from original sources.</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="15" hidden="0" customHeight="1">
+    <x:row r="8" ht="24" hidden="0" customHeight="1">
       <x:c r="A8" s="9" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>Unverified DOI, ORCID, email, and repository-code fields are omitted rather than fabricated.</x:v>
+        <x:v>The owner-confirmed repository URL is recorded; unverified DOI, ORCID, and email fields remain omitted rather than fabricated.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -525,7 +525,7 @@
     <x:col min="3" max="3" width="10" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="38" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="38" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="17" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="10" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -628,7 +628,7 @@
         <x:v>PASS</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="24" hidden="0" customHeight="1">
+    <x:row r="6" ht="36" hidden="0" customHeight="1">
       <x:c r="A6" s="32" t="str">
         <x:v>Must publish</x:v>
       </x:c>
@@ -642,13 +642,13 @@
         <x:v>environment/; docs/environment_validation_report.md</x:v>
       </x:c>
       <x:c r="E6" s="32" t="str">
-        <x:v>Versions and seeds are recorded; checked-in renv.lock remains incomplete</x:v>
+        <x:v>Seeds are recorded; the 188-package R 4.5.2/Bioconductor 3.22 lock passed a non-no-op clean-project restore and status check</x:v>
       </x:c>
       <x:c r="F6" s="32" t="str">
-        <x:v>PASS WITH LIMITATION</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="36" hidden="0" customHeight="1">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="48" hidden="0" customHeight="1">
       <x:c r="A7" s="32" t="str">
         <x:v>Must publish</x:v>
       </x:c>
@@ -662,7 +662,7 @@
         <x:v>repository root</x:v>
       </x:c>
       <x:c r="E7" s="32" t="str">
-        <x:v>CITATION.cff and both Zenodo JSON files are synchronized without fabricated DOI, ORCID, email, or repository-code fields</x:v>
+        <x:v>CITATION.cff and Zenodo JSON metadata are synchronized; the real owner-confirmed repository URL is recorded without fabricated DOI, ORCID, or email fields</x:v>
       </x:c>
       <x:c r="F7" s="32" t="str">
         <x:v>PASS</x:v>
@@ -759,10 +759,10 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="D12" s="32" t="str">
-        <x:v>DOI, ORCID, email, unverified repository-code</x:v>
+        <x:v>DOI, ORCID, email</x:v>
       </x:c>
       <x:c r="E12" s="32" t="str">
-        <x:v>Identifier fields remain omitted until independently verified</x:v>
+        <x:v>Unverified identifier fields remain omitted rather than fabricated</x:v>
       </x:c>
       <x:c r="F12" s="32" t="str">
         <x:v>EXCLUDED</x:v>
@@ -796,7 +796,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd72d07eda054ca6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d3fad910c2f4e95"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/PUBLIC_PRIVATE_CHECKLIST.xlsx
+++ b/PUBLIC_PRIVATE_CHECKLIST.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rf173b6e78e1342b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R7f71eae8edae4225"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R19e0534370374fac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="Raf3ea0ba4f6c4dff"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,7 +14,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="7">
+  <x:fonts count="8">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -54,8 +54,14 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF006100"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="10">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -75,6 +81,31 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFDEDEC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -132,7 +163,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="40">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -203,6 +234,12 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -214,7 +251,7 @@
         <x:color rgb="FF1B7837"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE8F5E9"/>
         </x:patternFill>
       </x:fill>
@@ -225,7 +262,7 @@
         <x:color rgb="FF9B1C1C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDEDEC"/>
         </x:patternFill>
       </x:fill>
@@ -235,7 +272,7 @@
         <x:color rgb="FF9B1C1C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDEDEC"/>
         </x:patternFill>
       </x:fill>
@@ -468,14 +505,15 @@
       <x:c r="E1" s="3"/>
       <x:c r="F1" s="3"/>
     </x:row>
-    <x:row r="3">
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="5" t="str">
         <x:v>Overall status</x:v>
       </x:c>
-      <x:c r="B3" s="7" t="str">
-        <x:v>NOT READY</x:v>
-      </x:c>
-    </x:row>
+      <x:c r="B3" s="39" t="str">
+        <x:v>PUBLIC RELEASE AVAILABLE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4"/>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="9" t="n">
         <x:v>1</x:v>
@@ -505,7 +543,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>The owner-confirmed repository URL is recorded; unverified DOI, ORCID, and email fields remain omitted rather than fabricated.</x:v>
+        <x:v>The public repository URL and verified Zenodo DOIs are recorded; unverified ORCID and email fields remain omitted rather than fabricated.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -648,7 +686,7 @@
         <x:v>PASS</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="48" hidden="0" customHeight="1">
+    <x:row r="7" ht="60" hidden="0" customHeight="1">
       <x:c r="A7" s="32" t="str">
         <x:v>Must publish</x:v>
       </x:c>
@@ -662,7 +700,7 @@
         <x:v>repository root</x:v>
       </x:c>
       <x:c r="E7" s="32" t="str">
-        <x:v>CITATION.cff and Zenodo JSON metadata are synchronized; the real owner-confirmed repository URL is recorded without fabricated DOI, ORCID, or email fields</x:v>
+        <x:v>CITATION.cff and Zenodo JSON metadata record the verified public repository, v1.0.0, version DOI 10.5281/zenodo.21762839, and concept DOI 10.5281/zenodo.21762838; ORCID and email remain omitted.</x:v>
       </x:c>
       <x:c r="F7" s="32" t="str">
         <x:v>PASS</x:v>
@@ -753,16 +791,16 @@
         <x:v>Do not upload</x:v>
       </x:c>
       <x:c r="B12" s="32" t="str">
-        <x:v>Unverified identifiers</x:v>
+        <x:v>Unverified personal identifiers</x:v>
       </x:c>
       <x:c r="C12" s="32" t="str">
         <x:v>No</x:v>
       </x:c>
       <x:c r="D12" s="32" t="str">
-        <x:v>DOI, ORCID, email</x:v>
+        <x:v>ORCID, email</x:v>
       </x:c>
       <x:c r="E12" s="32" t="str">
-        <x:v>Unverified identifier fields remain omitted rather than fabricated</x:v>
+        <x:v>Unverified personal identifiers remain omitted rather than fabricated</x:v>
       </x:c>
       <x:c r="F12" s="32" t="str">
         <x:v>EXCLUDED</x:v>
@@ -796,7 +834,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d3fad910c2f4e95"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41cab238a1c84570"/>
   </x:tableParts>
 </x:worksheet>
 </file>